--- a/docs/ValueSet-BRPosicaoIndividuo.xlsx
+++ b/docs/ValueSet-BRPosicaoIndividuo.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -124,19 +124,19 @@
     <t>LA11868-9</t>
   </si>
   <si>
-    <t>Sentado</t>
+    <t>Sitting</t>
   </si>
   <si>
     <t>LA11869-7</t>
   </si>
   <si>
-    <t>Deitado</t>
+    <t>Lying</t>
   </si>
   <si>
     <t>LA11870-5</t>
   </si>
   <si>
-    <t>De pé</t>
+    <t>Standing</t>
   </si>
   <si>
     <t>http://loinc.org</t>
